--- a/data/meta_analysis/old/Cat meta-analysis - correlations.xlsx
+++ b/data/meta_analysis/old/Cat meta-analysis - correlations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/iucn_evidence/CATS/data/meta_analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/iucn_evidence/cat_evidence_review/data/meta_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128F564A-E351-9E4E-A688-491617E1894B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A6740A-6F0A-6841-A6B7-0F9917DAB7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29380" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29380" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Correlations" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5709" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5998" uniqueCount="226">
   <si>
     <t>scientificName</t>
   </si>
@@ -692,28 +692,25 @@
     <t>Howland</t>
   </si>
   <si>
-    <t>SMD</t>
-  </si>
-  <si>
-    <t>Before-after eradication abundance</t>
-  </si>
-  <si>
     <t>ES_47b</t>
   </si>
   <si>
     <t>Baker</t>
   </si>
   <si>
-    <t>ES_ARM</t>
+    <t>unit_of_replication</t>
   </si>
   <si>
-    <t>Peromyscus pseudocrinitus</t>
+    <t>Plots</t>
   </si>
   <si>
-    <t>Rodríguez-Moreno A, Arnaud G, Tershy BR (2007) Impacto de la eradicación del gato (Felis catus), en dos roedores endémicos de la Isla Coronados, Golfo de California, México. Acta Zoológica Mexicana, 23, 1-13.</t>
+    <t>Sites</t>
   </si>
   <si>
-    <t>Isla Coronados, Gulf of California</t>
+    <t>Nests</t>
+  </si>
+  <si>
+    <t>Surveys</t>
   </si>
 </sst>
 </file>
@@ -881,7 +878,7 @@
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1146,7 +1143,16 @@
     <xf numFmtId="17" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="17" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2280,7 +2286,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AO493"/>
+  <dimension ref="A1:AO481"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -2307,7 +2313,7 @@
     <col min="24" max="16384" width="8.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>128</v>
       </c>
@@ -2374,8 +2380,11 @@
       <c r="V1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W1" s="88" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>129</v>
       </c>
@@ -2430,8 +2439,11 @@
       <c r="V2" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W2" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>129</v>
       </c>
@@ -2486,8 +2498,11 @@
       <c r="V3" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W3" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>129</v>
       </c>
@@ -2542,8 +2557,11 @@
       <c r="V4" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W4" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>129</v>
       </c>
@@ -2598,8 +2616,11 @@
       <c r="V5" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W5" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>129</v>
       </c>
@@ -2654,8 +2675,11 @@
       <c r="V6" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W6" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>129</v>
       </c>
@@ -2710,8 +2734,11 @@
       <c r="V7" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W7" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="22" t="s">
         <v>130</v>
       </c>
@@ -2766,8 +2793,11 @@
       <c r="V8" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W8" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="22" t="s">
         <v>130</v>
       </c>
@@ -2822,8 +2852,11 @@
       <c r="V9" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W9" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="22" t="s">
         <v>130</v>
       </c>
@@ -2878,8 +2911,11 @@
       <c r="V10" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W10" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="22" t="s">
         <v>130</v>
       </c>
@@ -2934,8 +2970,11 @@
       <c r="V11" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W11" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="22" t="s">
         <v>130</v>
       </c>
@@ -2990,8 +3029,11 @@
       <c r="V12" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W12" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="22" t="s">
         <v>130</v>
       </c>
@@ -3046,8 +3088,11 @@
       <c r="V13" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W13" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="22" t="s">
         <v>130</v>
       </c>
@@ -3102,8 +3147,11 @@
       <c r="V14" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W14" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="22" t="s">
         <v>130</v>
       </c>
@@ -3158,8 +3206,11 @@
       <c r="V15" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W15" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="22" t="s">
         <v>130</v>
       </c>
@@ -3214,8 +3265,11 @@
       <c r="V16" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W16" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="22" t="s">
         <v>130</v>
       </c>
@@ -3270,8 +3324,11 @@
       <c r="V17" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W17" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="22" t="s">
         <v>130</v>
       </c>
@@ -3326,8 +3383,11 @@
       <c r="V18" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W18" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="22" t="s">
         <v>130</v>
       </c>
@@ -3382,8 +3442,11 @@
       <c r="V19" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W19" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="22" t="s">
         <v>130</v>
       </c>
@@ -3438,8 +3501,11 @@
       <c r="V20" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W20" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
         <v>131</v>
       </c>
@@ -3494,8 +3560,11 @@
       <c r="V21" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W21" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
         <v>131</v>
       </c>
@@ -3550,8 +3619,11 @@
       <c r="V22" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W22" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
         <v>131</v>
       </c>
@@ -3606,8 +3678,11 @@
       <c r="V23" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W23" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
         <v>131</v>
       </c>
@@ -3662,8 +3737,11 @@
       <c r="V24" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W24" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
         <v>131</v>
       </c>
@@ -3718,8 +3796,11 @@
       <c r="V25" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W25" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
         <v>131</v>
       </c>
@@ -3774,8 +3855,11 @@
       <c r="V26" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W26" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
         <v>131</v>
       </c>
@@ -3830,8 +3914,11 @@
       <c r="V27" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W27" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>131</v>
       </c>
@@ -3886,8 +3973,11 @@
       <c r="V28" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W28" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
         <v>131</v>
       </c>
@@ -3942,8 +4032,11 @@
       <c r="V29" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W29" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>131</v>
       </c>
@@ -3998,8 +4091,11 @@
       <c r="V30" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W30" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>131</v>
       </c>
@@ -4054,8 +4150,11 @@
       <c r="V31" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W31" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>131</v>
       </c>
@@ -4110,8 +4209,11 @@
       <c r="V32" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W32" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="22" t="s">
         <v>132</v>
       </c>
@@ -4168,8 +4270,11 @@
       <c r="V33" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W33" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="22" t="s">
         <v>132</v>
       </c>
@@ -4226,8 +4331,11 @@
       <c r="V34" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W34" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="22" t="s">
         <v>132</v>
       </c>
@@ -4284,8 +4392,11 @@
       <c r="V35" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W35" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="22" t="s">
         <v>132</v>
       </c>
@@ -4342,8 +4453,11 @@
       <c r="V36" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W36" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="22" t="s">
         <v>132</v>
       </c>
@@ -4400,8 +4514,11 @@
       <c r="V37" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="38" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W37" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="22" t="s">
         <v>132</v>
       </c>
@@ -4458,8 +4575,11 @@
       <c r="V38" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W38" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="22" t="s">
         <v>132</v>
       </c>
@@ -4516,8 +4636,11 @@
       <c r="V39" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W39" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="22" t="s">
         <v>132</v>
       </c>
@@ -4574,8 +4697,11 @@
       <c r="V40" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W40" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="22" t="s">
         <v>132</v>
       </c>
@@ -4632,8 +4758,11 @@
       <c r="V41" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W41" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="22" t="s">
         <v>132</v>
       </c>
@@ -4690,8 +4819,11 @@
       <c r="V42" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="43" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W42" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="22" t="s">
         <v>132</v>
       </c>
@@ -4748,8 +4880,11 @@
       <c r="V43" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W43" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="22" t="s">
         <v>132</v>
       </c>
@@ -4806,8 +4941,11 @@
       <c r="V44" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W44" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="22" t="s">
         <v>132</v>
       </c>
@@ -4864,8 +5002,11 @@
       <c r="V45" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="46" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W45" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="22" t="s">
         <v>132</v>
       </c>
@@ -4922,8 +5063,11 @@
       <c r="V46" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W46" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="22" t="s">
         <v>132</v>
       </c>
@@ -4980,8 +5124,11 @@
       <c r="V47" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W47" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="22" t="s">
         <v>132</v>
       </c>
@@ -5038,8 +5185,11 @@
       <c r="V48" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="49" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W48" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="22" t="s">
         <v>132</v>
       </c>
@@ -5096,8 +5246,11 @@
       <c r="V49" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="50" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W49" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="22" t="s">
         <v>132</v>
       </c>
@@ -5154,8 +5307,11 @@
       <c r="V50" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="51" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W50" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="22" t="s">
         <v>132</v>
       </c>
@@ -5212,8 +5368,11 @@
       <c r="V51" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="52" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W51" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="22" t="s">
         <v>132</v>
       </c>
@@ -5270,8 +5429,11 @@
       <c r="V52" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="53" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W52" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="22" t="s">
         <v>132</v>
       </c>
@@ -5328,8 +5490,11 @@
       <c r="V53" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W53" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="22" t="s">
         <v>132</v>
       </c>
@@ -5386,8 +5551,11 @@
       <c r="V54" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="55" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W54" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="22" t="s">
         <v>132</v>
       </c>
@@ -5444,8 +5612,11 @@
       <c r="V55" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="56" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W55" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="22" t="s">
         <v>132</v>
       </c>
@@ -5502,8 +5673,11 @@
       <c r="V56" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="57" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W56" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
         <v>133</v>
       </c>
@@ -5560,8 +5734,11 @@
       <c r="V57" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="58" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W57" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
         <v>133</v>
       </c>
@@ -5618,8 +5795,11 @@
       <c r="V58" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="59" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W58" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
         <v>133</v>
       </c>
@@ -5676,8 +5856,11 @@
       <c r="V59" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="60" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W59" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
         <v>133</v>
       </c>
@@ -5734,8 +5917,11 @@
       <c r="V60" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="61" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W60" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
         <v>133</v>
       </c>
@@ -5792,8 +5978,11 @@
       <c r="V61" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="62" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W61" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
         <v>133</v>
       </c>
@@ -5850,8 +6039,11 @@
       <c r="V62" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="63" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W62" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
         <v>133</v>
       </c>
@@ -5908,8 +6100,11 @@
       <c r="V63" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="64" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W63" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
         <v>133</v>
       </c>
@@ -5966,8 +6161,11 @@
       <c r="V64" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="65" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W64" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
         <v>133</v>
       </c>
@@ -6024,8 +6222,11 @@
       <c r="V65" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="66" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W65" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
         <v>133</v>
       </c>
@@ -6082,8 +6283,11 @@
       <c r="V66" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="67" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W66" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
         <v>133</v>
       </c>
@@ -6140,8 +6344,11 @@
       <c r="V67" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="68" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W67" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
         <v>133</v>
       </c>
@@ -6198,8 +6405,11 @@
       <c r="V68" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="69" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W68" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
         <v>133</v>
       </c>
@@ -6256,8 +6466,11 @@
       <c r="V69" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="70" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W69" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
         <v>133</v>
       </c>
@@ -6314,8 +6527,11 @@
       <c r="V70" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="71" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W70" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
         <v>133</v>
       </c>
@@ -6372,8 +6588,11 @@
       <c r="V71" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="72" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W71" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
         <v>133</v>
       </c>
@@ -6430,8 +6649,11 @@
       <c r="V72" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="73" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W72" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
         <v>133</v>
       </c>
@@ -6488,8 +6710,11 @@
       <c r="V73" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="74" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W73" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
         <v>133</v>
       </c>
@@ -6546,8 +6771,11 @@
       <c r="V74" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="75" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W74" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
         <v>133</v>
       </c>
@@ -6604,8 +6832,11 @@
       <c r="V75" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="76" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W75" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
         <v>133</v>
       </c>
@@ -6662,8 +6893,11 @@
       <c r="V76" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="77" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W76" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
         <v>133</v>
       </c>
@@ -6720,8 +6954,11 @@
       <c r="V77" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="78" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W77" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
         <v>133</v>
       </c>
@@ -6778,8 +7015,11 @@
       <c r="V78" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W78" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
         <v>133</v>
       </c>
@@ -6836,8 +7076,11 @@
       <c r="V79" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="80" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W79" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
         <v>133</v>
       </c>
@@ -6894,8 +7137,11 @@
       <c r="V80" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="81" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W80" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="22" t="s">
         <v>134</v>
       </c>
@@ -6952,8 +7198,11 @@
       <c r="V81" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="82" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W81" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="22" t="s">
         <v>134</v>
       </c>
@@ -7010,8 +7259,11 @@
       <c r="V82" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="83" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W82" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="22" t="s">
         <v>134</v>
       </c>
@@ -7068,8 +7320,11 @@
       <c r="V83" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="84" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W83" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="22" t="s">
         <v>134</v>
       </c>
@@ -7126,8 +7381,11 @@
       <c r="V84" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="85" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W84" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="22" t="s">
         <v>134</v>
       </c>
@@ -7184,8 +7442,11 @@
       <c r="V85" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W85" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="22" t="s">
         <v>134</v>
       </c>
@@ -7242,8 +7503,11 @@
       <c r="V86" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W86" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="22" t="s">
         <v>134</v>
       </c>
@@ -7300,8 +7564,11 @@
       <c r="V87" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="88" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W87" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="22" t="s">
         <v>134</v>
       </c>
@@ -7358,8 +7625,11 @@
       <c r="V88" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="89" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W88" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="22" t="s">
         <v>134</v>
       </c>
@@ -7416,8 +7686,11 @@
       <c r="V89" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="90" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W89" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="22" t="s">
         <v>134</v>
       </c>
@@ -7474,8 +7747,11 @@
       <c r="V90" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="91" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W90" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="22" t="s">
         <v>134</v>
       </c>
@@ -7532,8 +7808,11 @@
       <c r="V91" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="92" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W91" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="22" t="s">
         <v>134</v>
       </c>
@@ -7590,8 +7869,11 @@
       <c r="V92" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="93" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W92" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="22" t="s">
         <v>134</v>
       </c>
@@ -7648,8 +7930,11 @@
       <c r="V93" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="94" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W93" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="22" t="s">
         <v>134</v>
       </c>
@@ -7706,8 +7991,11 @@
       <c r="V94" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="95" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W94" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="22" t="s">
         <v>134</v>
       </c>
@@ -7764,8 +8052,11 @@
       <c r="V95" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="96" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W95" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="22" t="s">
         <v>134</v>
       </c>
@@ -7822,8 +8113,11 @@
       <c r="V96" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W96" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="22" t="s">
         <v>134</v>
       </c>
@@ -7880,8 +8174,11 @@
       <c r="V97" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="98" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W97" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="22" t="s">
         <v>134</v>
       </c>
@@ -7938,8 +8235,11 @@
       <c r="V98" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="99" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W98" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="22" t="s">
         <v>134</v>
       </c>
@@ -7996,8 +8296,11 @@
       <c r="V99" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="100" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W99" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="22" t="s">
         <v>134</v>
       </c>
@@ -8054,8 +8357,11 @@
       <c r="V100" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="101" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W100" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="22" t="s">
         <v>134</v>
       </c>
@@ -8112,8 +8418,11 @@
       <c r="V101" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="102" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W101" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="22" t="s">
         <v>134</v>
       </c>
@@ -8170,8 +8479,11 @@
       <c r="V102" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="103" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W102" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="22" t="s">
         <v>134</v>
       </c>
@@ -8228,8 +8540,11 @@
       <c r="V103" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="104" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W103" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="22" t="s">
         <v>134</v>
       </c>
@@ -8286,8 +8601,11 @@
       <c r="V104" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="105" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W104" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="8" t="s">
         <v>135</v>
       </c>
@@ -8344,8 +8662,11 @@
       <c r="V105" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="106" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W105" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="8" t="s">
         <v>135</v>
       </c>
@@ -8402,8 +8723,11 @@
       <c r="V106" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="107" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W106" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="8" t="s">
         <v>135</v>
       </c>
@@ -8460,8 +8784,11 @@
       <c r="V107" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="108" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W107" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="8" t="s">
         <v>135</v>
       </c>
@@ -8518,8 +8845,11 @@
       <c r="V108" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="109" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W108" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="8" t="s">
         <v>135</v>
       </c>
@@ -8576,8 +8906,11 @@
       <c r="V109" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="110" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W109" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="8" t="s">
         <v>135</v>
       </c>
@@ -8634,8 +8967,11 @@
       <c r="V110" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="111" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W110" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="8" t="s">
         <v>135</v>
       </c>
@@ -8692,8 +9028,11 @@
       <c r="V111" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="112" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W111" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="8" t="s">
         <v>135</v>
       </c>
@@ -8750,8 +9089,11 @@
       <c r="V112" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="113" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W112" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="22" t="s">
         <v>136</v>
       </c>
@@ -8808,8 +9150,11 @@
       <c r="V113" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="114" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W113" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="22" t="s">
         <v>136</v>
       </c>
@@ -8866,8 +9211,11 @@
       <c r="V114" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="115" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W114" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="22" t="s">
         <v>136</v>
       </c>
@@ -8924,8 +9272,11 @@
       <c r="V115" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="116" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W115" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="22" t="s">
         <v>136</v>
       </c>
@@ -8982,8 +9333,11 @@
       <c r="V116" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="117" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W116" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="22" t="s">
         <v>136</v>
       </c>
@@ -9040,8 +9394,11 @@
       <c r="V117" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="118" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W117" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="22" t="s">
         <v>136</v>
       </c>
@@ -9098,8 +9455,11 @@
       <c r="V118" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="119" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W118" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="22" t="s">
         <v>136</v>
       </c>
@@ -9156,8 +9516,11 @@
       <c r="V119" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="120" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W119" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="22" t="s">
         <v>136</v>
       </c>
@@ -9214,8 +9577,11 @@
       <c r="V120" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="121" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W120" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="8" t="s">
         <v>137</v>
       </c>
@@ -9270,8 +9636,11 @@
       <c r="V121" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="122" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W121" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="8" t="s">
         <v>137</v>
       </c>
@@ -9326,8 +9695,11 @@
       <c r="V122" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="123" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W122" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="8" t="s">
         <v>137</v>
       </c>
@@ -9382,8 +9754,11 @@
       <c r="V123" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="124" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W123" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="8" t="s">
         <v>137</v>
       </c>
@@ -9438,8 +9813,11 @@
       <c r="V124" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="125" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W124" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="8" t="s">
         <v>137</v>
       </c>
@@ -9494,8 +9872,11 @@
       <c r="V125" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="126" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W125" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="8" t="s">
         <v>137</v>
       </c>
@@ -9550,8 +9931,11 @@
       <c r="V126" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="127" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W126" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="8" t="s">
         <v>137</v>
       </c>
@@ -9606,8 +9990,11 @@
       <c r="V127" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="128" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W127" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="8" t="s">
         <v>137</v>
       </c>
@@ -9662,8 +10049,11 @@
       <c r="V128" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="129" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W128" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="8" t="s">
         <v>137</v>
       </c>
@@ -9718,8 +10108,11 @@
       <c r="V129" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="130" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W129" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="8" t="s">
         <v>137</v>
       </c>
@@ -9774,8 +10167,11 @@
       <c r="V130" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="131" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W130" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="8" t="s">
         <v>137</v>
       </c>
@@ -9830,8 +10226,11 @@
       <c r="V131" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="132" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W131" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="8" t="s">
         <v>137</v>
       </c>
@@ -9886,8 +10285,11 @@
       <c r="V132" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="133" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W132" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="8" t="s">
         <v>137</v>
       </c>
@@ -9942,8 +10344,11 @@
       <c r="V133" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="134" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W133" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="8" t="s">
         <v>137</v>
       </c>
@@ -9998,8 +10403,11 @@
       <c r="V134" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="135" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W134" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="8" t="s">
         <v>137</v>
       </c>
@@ -10054,8 +10462,11 @@
       <c r="V135" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="136" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W135" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="8" t="s">
         <v>137</v>
       </c>
@@ -10110,8 +10521,11 @@
       <c r="V136" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="137" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W136" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="8" t="s">
         <v>137</v>
       </c>
@@ -10166,8 +10580,11 @@
       <c r="V137" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="138" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W137" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="8" t="s">
         <v>137</v>
       </c>
@@ -10222,8 +10639,11 @@
       <c r="V138" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="139" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W138" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="8" t="s">
         <v>137</v>
       </c>
@@ -10278,8 +10698,11 @@
       <c r="V139" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="140" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W139" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="8" t="s">
         <v>137</v>
       </c>
@@ -10334,8 +10757,11 @@
       <c r="V140" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="141" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W140" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="8" t="s">
         <v>137</v>
       </c>
@@ -10390,8 +10816,11 @@
       <c r="V141" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="142" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W141" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="8" t="s">
         <v>137</v>
       </c>
@@ -10446,8 +10875,11 @@
       <c r="V142" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="143" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W142" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="8" t="s">
         <v>137</v>
       </c>
@@ -10502,8 +10934,11 @@
       <c r="V143" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="144" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W143" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="8" t="s">
         <v>137</v>
       </c>
@@ -10558,8 +10993,11 @@
       <c r="V144" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="145" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W144" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="8" t="s">
         <v>137</v>
       </c>
@@ -10614,8 +11052,11 @@
       <c r="V145" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="146" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W145" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="8" t="s">
         <v>137</v>
       </c>
@@ -10670,8 +11111,11 @@
       <c r="V146" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="147" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W146" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="8" t="s">
         <v>137</v>
       </c>
@@ -10726,8 +11170,11 @@
       <c r="V147" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="148" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W147" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="8" t="s">
         <v>137</v>
       </c>
@@ -10782,8 +11229,11 @@
       <c r="V148" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="149" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W148" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="8" t="s">
         <v>137</v>
       </c>
@@ -10838,8 +11288,11 @@
       <c r="V149" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="150" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W149" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="8" t="s">
         <v>137</v>
       </c>
@@ -10894,8 +11347,11 @@
       <c r="V150" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="151" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W150" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="8" t="s">
         <v>137</v>
       </c>
@@ -10950,8 +11406,11 @@
       <c r="V151" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="152" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W151" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="8" t="s">
         <v>137</v>
       </c>
@@ -11006,8 +11465,11 @@
       <c r="V152" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="153" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W152" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="8" t="s">
         <v>137</v>
       </c>
@@ -11062,8 +11524,11 @@
       <c r="V153" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="154" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W153" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="8" t="s">
         <v>137</v>
       </c>
@@ -11118,8 +11583,11 @@
       <c r="V154" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="155" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W154" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="8" t="s">
         <v>137</v>
       </c>
@@ -11174,8 +11642,11 @@
       <c r="V155" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="156" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W155" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="8" t="s">
         <v>137</v>
       </c>
@@ -11230,8 +11701,11 @@
       <c r="V156" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="157" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W156" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="8" t="s">
         <v>137</v>
       </c>
@@ -11286,8 +11760,11 @@
       <c r="V157" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="158" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W157" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="8" t="s">
         <v>137</v>
       </c>
@@ -11342,8 +11819,11 @@
       <c r="V158" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="159" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W158" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="8" t="s">
         <v>137</v>
       </c>
@@ -11398,8 +11878,11 @@
       <c r="V159" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="160" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W159" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="8" t="s">
         <v>137</v>
       </c>
@@ -11454,8 +11937,11 @@
       <c r="V160" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="161" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W160" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="8" t="s">
         <v>137</v>
       </c>
@@ -11510,8 +11996,11 @@
       <c r="V161" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="162" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W161" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="8" t="s">
         <v>137</v>
       </c>
@@ -11566,8 +12055,11 @@
       <c r="V162" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="163" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W162" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="8" t="s">
         <v>137</v>
       </c>
@@ -11622,8 +12114,11 @@
       <c r="V163" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="164" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W163" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="8" t="s">
         <v>137</v>
       </c>
@@ -11678,8 +12173,11 @@
       <c r="V164" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="165" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W164" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="8" t="s">
         <v>137</v>
       </c>
@@ -11734,8 +12232,11 @@
       <c r="V165" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="166" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W165" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="8" t="s">
         <v>137</v>
       </c>
@@ -11790,8 +12291,11 @@
       <c r="V166" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="167" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W166" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="8" t="s">
         <v>137</v>
       </c>
@@ -11846,8 +12350,11 @@
       <c r="V167" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="168" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W167" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="8" t="s">
         <v>137</v>
       </c>
@@ -11902,8 +12409,11 @@
       <c r="V168" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="169" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W168" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="8" t="s">
         <v>137</v>
       </c>
@@ -11958,8 +12468,11 @@
       <c r="V169" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="170" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W169" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="8" t="s">
         <v>137</v>
       </c>
@@ -12014,8 +12527,11 @@
       <c r="V170" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="171" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W170" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="8" t="s">
         <v>137</v>
       </c>
@@ -12070,8 +12586,11 @@
       <c r="V171" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="172" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W171" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="8" t="s">
         <v>137</v>
       </c>
@@ -12126,8 +12645,11 @@
       <c r="V172" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="173" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W172" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="8" t="s">
         <v>137</v>
       </c>
@@ -12182,8 +12704,11 @@
       <c r="V173" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="174" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W173" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="8" t="s">
         <v>137</v>
       </c>
@@ -12238,8 +12763,11 @@
       <c r="V174" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="175" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W174" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="22" t="s">
         <v>138</v>
       </c>
@@ -12296,8 +12824,11 @@
       <c r="V175" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="176" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W175" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="22" t="s">
         <v>138</v>
       </c>
@@ -12354,8 +12885,11 @@
       <c r="V176" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="177" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W176" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="22" t="s">
         <v>138</v>
       </c>
@@ -12412,8 +12946,11 @@
       <c r="V177" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="178" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W177" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="22" t="s">
         <v>138</v>
       </c>
@@ -12470,8 +13007,11 @@
       <c r="V178" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="179" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W178" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="22" t="s">
         <v>138</v>
       </c>
@@ -12528,8 +13068,11 @@
       <c r="V179" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="180" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W179" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="22" t="s">
         <v>138</v>
       </c>
@@ -12586,8 +13129,11 @@
       <c r="V180" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="181" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W180" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="8" t="s">
         <v>139</v>
       </c>
@@ -12642,8 +13188,11 @@
       <c r="V181" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="182" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W181" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="8" t="s">
         <v>139</v>
       </c>
@@ -12698,8 +13247,11 @@
       <c r="V182" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="183" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W182" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="8" t="s">
         <v>139</v>
       </c>
@@ -12754,8 +13306,11 @@
       <c r="V183" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="184" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W183" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="8" t="s">
         <v>139</v>
       </c>
@@ -12810,8 +13365,11 @@
       <c r="V184" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="185" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W184" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="8" t="s">
         <v>139</v>
       </c>
@@ -12866,8 +13424,11 @@
       <c r="V185" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="186" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W185" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="8" t="s">
         <v>139</v>
       </c>
@@ -12922,8 +13483,11 @@
       <c r="V186" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="187" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W186" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="8" t="s">
         <v>139</v>
       </c>
@@ -12978,8 +13542,11 @@
       <c r="V187" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="188" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W187" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="8" t="s">
         <v>139</v>
       </c>
@@ -13034,8 +13601,11 @@
       <c r="V188" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="189" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W188" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="8" t="s">
         <v>139</v>
       </c>
@@ -13090,8 +13660,11 @@
       <c r="V189" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="190" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W189" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="8" t="s">
         <v>139</v>
       </c>
@@ -13146,8 +13719,11 @@
       <c r="V190" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="191" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W190" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="8" t="s">
         <v>139</v>
       </c>
@@ -13202,8 +13778,11 @@
       <c r="V191" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="192" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W191" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="8" t="s">
         <v>139</v>
       </c>
@@ -13258,8 +13837,11 @@
       <c r="V192" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="193" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W192" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="8" t="s">
         <v>139</v>
       </c>
@@ -13314,8 +13896,11 @@
       <c r="V193" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="194" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W193" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="8" t="s">
         <v>139</v>
       </c>
@@ -13370,8 +13955,11 @@
       <c r="V194" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="195" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W194" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="8" t="s">
         <v>139</v>
       </c>
@@ -13426,8 +14014,11 @@
       <c r="V195" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="196" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W195" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="8" t="s">
         <v>139</v>
       </c>
@@ -13482,8 +14073,11 @@
       <c r="V196" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="197" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W196" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="8" t="s">
         <v>139</v>
       </c>
@@ -13538,8 +14132,11 @@
       <c r="V197" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="198" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W197" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="8" t="s">
         <v>139</v>
       </c>
@@ -13594,8 +14191,11 @@
       <c r="V198" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="199" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W198" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="8" t="s">
         <v>139</v>
       </c>
@@ -13650,8 +14250,11 @@
       <c r="V199" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="200" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W199" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="8" t="s">
         <v>139</v>
       </c>
@@ -13706,8 +14309,11 @@
       <c r="V200" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="201" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W200" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="8" t="s">
         <v>139</v>
       </c>
@@ -13762,8 +14368,11 @@
       <c r="V201" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="202" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W201" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="8" t="s">
         <v>139</v>
       </c>
@@ -13818,8 +14427,11 @@
       <c r="V202" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="203" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W202" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="8" t="s">
         <v>139</v>
       </c>
@@ -13874,8 +14486,11 @@
       <c r="V203" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="204" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W203" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="8" t="s">
         <v>139</v>
       </c>
@@ -13930,8 +14545,11 @@
       <c r="V204" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="205" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W204" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="8" t="s">
         <v>139</v>
       </c>
@@ -13986,8 +14604,11 @@
       <c r="V205" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="206" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W205" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="8" t="s">
         <v>139</v>
       </c>
@@ -14042,8 +14663,11 @@
       <c r="V206" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="207" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W206" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="207" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="8" t="s">
         <v>139</v>
       </c>
@@ -14098,8 +14722,11 @@
       <c r="V207" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="208" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W207" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="208" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="8" t="s">
         <v>139</v>
       </c>
@@ -14154,8 +14781,11 @@
       <c r="V208" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="209" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W208" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="209" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="8" t="s">
         <v>139</v>
       </c>
@@ -14210,8 +14840,11 @@
       <c r="V209" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="210" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W209" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="210" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="8" t="s">
         <v>139</v>
       </c>
@@ -14266,8 +14899,11 @@
       <c r="V210" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="211" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W210" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="211" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="8" t="s">
         <v>139</v>
       </c>
@@ -14322,8 +14958,11 @@
       <c r="V211" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="212" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W211" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="212" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="8" t="s">
         <v>139</v>
       </c>
@@ -14378,8 +15017,11 @@
       <c r="V212" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="213" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W212" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="213" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="8" t="s">
         <v>139</v>
       </c>
@@ -14434,8 +15076,11 @@
       <c r="V213" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="214" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W213" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="214" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="8" t="s">
         <v>139</v>
       </c>
@@ -14490,8 +15135,11 @@
       <c r="V214" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="215" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W214" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="215" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="8" t="s">
         <v>139</v>
       </c>
@@ -14546,8 +15194,11 @@
       <c r="V215" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="216" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W215" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="216" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="8" t="s">
         <v>139</v>
       </c>
@@ -14602,8 +15253,11 @@
       <c r="V216" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="217" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W216" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="217" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="8" t="s">
         <v>139</v>
       </c>
@@ -14658,8 +15312,11 @@
       <c r="V217" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="218" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W217" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="8" t="s">
         <v>139</v>
       </c>
@@ -14714,8 +15371,11 @@
       <c r="V218" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="219" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W218" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="8" t="s">
         <v>139</v>
       </c>
@@ -14770,8 +15430,11 @@
       <c r="V219" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="220" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W219" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="8" t="s">
         <v>139</v>
       </c>
@@ -14826,8 +15489,11 @@
       <c r="V220" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="221" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W220" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="8" t="s">
         <v>139</v>
       </c>
@@ -14882,8 +15548,11 @@
       <c r="V221" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="222" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W221" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="222" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="8" t="s">
         <v>139</v>
       </c>
@@ -14938,8 +15607,11 @@
       <c r="V222" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="223" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W222" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="223" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="8" t="s">
         <v>139</v>
       </c>
@@ -14994,8 +15666,11 @@
       <c r="V223" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="224" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W223" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="8" t="s">
         <v>139</v>
       </c>
@@ -15050,8 +15725,11 @@
       <c r="V224" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="225" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W224" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="225" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="8" t="s">
         <v>139</v>
       </c>
@@ -15106,8 +15784,11 @@
       <c r="V225" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="226" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W225" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="226" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="22" t="s">
         <v>140</v>
       </c>
@@ -15162,8 +15843,11 @@
       <c r="V226" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="227" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W226" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="227" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="22" t="s">
         <v>140</v>
       </c>
@@ -15218,8 +15902,11 @@
       <c r="V227" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="228" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W227" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="228" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="22" t="s">
         <v>140</v>
       </c>
@@ -15274,8 +15961,11 @@
       <c r="V228" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="229" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W228" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="229" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="22" t="s">
         <v>140</v>
       </c>
@@ -15330,8 +16020,11 @@
       <c r="V229" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="230" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W229" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="230" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="22" t="s">
         <v>140</v>
       </c>
@@ -15386,8 +16079,11 @@
       <c r="V230" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="231" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W230" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="22" t="s">
         <v>140</v>
       </c>
@@ -15442,8 +16138,11 @@
       <c r="V231" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="232" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W231" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="232" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="22" t="s">
         <v>140</v>
       </c>
@@ -15498,8 +16197,11 @@
       <c r="V232" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="233" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W232" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="233" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="22" t="s">
         <v>140</v>
       </c>
@@ -15554,8 +16256,11 @@
       <c r="V233" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="234" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W233" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="234" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="22" t="s">
         <v>140</v>
       </c>
@@ -15610,8 +16315,11 @@
       <c r="V234" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="235" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W234" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="22" t="s">
         <v>140</v>
       </c>
@@ -15666,8 +16374,11 @@
       <c r="V235" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="236" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W235" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="22" t="s">
         <v>140</v>
       </c>
@@ -15722,8 +16433,11 @@
       <c r="V236" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="237" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W236" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="22" t="s">
         <v>140</v>
       </c>
@@ -15778,8 +16492,11 @@
       <c r="V237" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="238" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W237" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="22" t="s">
         <v>140</v>
       </c>
@@ -15834,8 +16551,11 @@
       <c r="V238" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="239" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W238" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="22" t="s">
         <v>140</v>
       </c>
@@ -15890,8 +16610,11 @@
       <c r="V239" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="240" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W239" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="22" t="s">
         <v>140</v>
       </c>
@@ -15946,8 +16669,11 @@
       <c r="V240" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="241" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W240" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="22" t="s">
         <v>140</v>
       </c>
@@ -16002,8 +16728,11 @@
       <c r="V241" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="242" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W241" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="22" t="s">
         <v>140</v>
       </c>
@@ -16058,8 +16787,11 @@
       <c r="V242" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="243" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W242" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="243" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="22" t="s">
         <v>140</v>
       </c>
@@ -16114,8 +16846,11 @@
       <c r="V243" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="244" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W243" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="22" t="s">
         <v>140</v>
       </c>
@@ -16170,8 +16905,11 @@
       <c r="V244" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="245" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W244" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="22" t="s">
         <v>140</v>
       </c>
@@ -16226,8 +16964,11 @@
       <c r="V245" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="246" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W245" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="22" t="s">
         <v>140</v>
       </c>
@@ -16282,8 +17023,11 @@
       <c r="V246" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="247" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W246" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="247" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="22" t="s">
         <v>140</v>
       </c>
@@ -16338,8 +17082,11 @@
       <c r="V247" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="248" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W247" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="22" t="s">
         <v>140</v>
       </c>
@@ -16394,8 +17141,11 @@
       <c r="V248" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="249" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W248" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="22" t="s">
         <v>140</v>
       </c>
@@ -16450,8 +17200,11 @@
       <c r="V249" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="250" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W249" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="22" t="s">
         <v>140</v>
       </c>
@@ -16506,8 +17259,11 @@
       <c r="V250" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="251" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W250" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="8" t="s">
         <v>141</v>
       </c>
@@ -16562,8 +17318,11 @@
       <c r="V251" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="252" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W251" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="8" t="s">
         <v>141</v>
       </c>
@@ -16618,8 +17377,11 @@
       <c r="V252" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="253" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W252" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="8" t="s">
         <v>141</v>
       </c>
@@ -16674,8 +17436,11 @@
       <c r="V253" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="254" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W253" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="8" t="s">
         <v>141</v>
       </c>
@@ -16730,8 +17495,11 @@
       <c r="V254" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="255" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W254" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="8" t="s">
         <v>141</v>
       </c>
@@ -16786,8 +17554,11 @@
       <c r="V255" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="256" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W255" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="8" t="s">
         <v>141</v>
       </c>
@@ -16842,8 +17613,11 @@
       <c r="V256" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="257" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W256" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="8" t="s">
         <v>141</v>
       </c>
@@ -16898,8 +17672,11 @@
       <c r="V257" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="258" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W257" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="8" t="s">
         <v>141</v>
       </c>
@@ -16954,8 +17731,11 @@
       <c r="V258" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="259" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W258" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="22" t="s">
         <v>142</v>
       </c>
@@ -17010,8 +17790,11 @@
       <c r="V259" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="260" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W259" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="22" t="s">
         <v>142</v>
       </c>
@@ -17066,8 +17849,11 @@
       <c r="V260" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="261" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W260" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="22" t="s">
         <v>142</v>
       </c>
@@ -17122,8 +17908,11 @@
       <c r="V261" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="262" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W261" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="22" t="s">
         <v>142</v>
       </c>
@@ -17178,8 +17967,11 @@
       <c r="V262" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="263" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W262" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="22" t="s">
         <v>142</v>
       </c>
@@ -17234,8 +18026,11 @@
       <c r="V263" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="264" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W263" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="22" t="s">
         <v>142</v>
       </c>
@@ -17290,8 +18085,11 @@
       <c r="V264" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="265" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W264" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="22" t="s">
         <v>142</v>
       </c>
@@ -17346,8 +18144,11 @@
       <c r="V265" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="266" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W265" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="8" t="s">
         <v>143</v>
       </c>
@@ -17402,8 +18203,11 @@
       <c r="V266" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="267" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W266" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="8" t="s">
         <v>143</v>
       </c>
@@ -17458,8 +18262,11 @@
       <c r="V267" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="268" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W267" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="8" t="s">
         <v>143</v>
       </c>
@@ -17514,8 +18321,11 @@
       <c r="V268" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="269" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W268" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="269" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="8" t="s">
         <v>143</v>
       </c>
@@ -17570,8 +18380,11 @@
       <c r="V269" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="270" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W269" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="8" t="s">
         <v>143</v>
       </c>
@@ -17626,8 +18439,11 @@
       <c r="V270" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="271" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W270" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="271" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="8" t="s">
         <v>143</v>
       </c>
@@ -17682,8 +18498,11 @@
       <c r="V271" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="272" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W271" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="8" t="s">
         <v>143</v>
       </c>
@@ -17738,8 +18557,11 @@
       <c r="V272" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="273" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W272" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="273" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="8" t="s">
         <v>143</v>
       </c>
@@ -17794,8 +18616,11 @@
       <c r="V273" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="274" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W273" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="22" t="s">
         <v>144</v>
       </c>
@@ -17854,8 +18679,11 @@
       <c r="V274" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="275" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W274" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="22" t="s">
         <v>144</v>
       </c>
@@ -17914,8 +18742,11 @@
       <c r="V275" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="276" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W275" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="22" t="s">
         <v>144</v>
       </c>
@@ -17974,8 +18805,11 @@
       <c r="V276" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="277" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W276" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="22" t="s">
         <v>144</v>
       </c>
@@ -18034,8 +18868,11 @@
       <c r="V277" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="278" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W277" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="278" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="22" t="s">
         <v>144</v>
       </c>
@@ -18094,8 +18931,11 @@
       <c r="V278" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="279" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W278" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="279" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="22" t="s">
         <v>144</v>
       </c>
@@ -18154,8 +18994,11 @@
       <c r="V279" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="280" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W279" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="280" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="22" t="s">
         <v>144</v>
       </c>
@@ -18214,8 +19057,11 @@
       <c r="V280" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="281" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W280" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="281" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="8" t="s">
         <v>145</v>
       </c>
@@ -18272,8 +19118,11 @@
       <c r="V281" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="282" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W281" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="282" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="8" t="s">
         <v>145</v>
       </c>
@@ -18330,8 +19179,11 @@
       <c r="V282" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="283" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W282" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="283" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="8" t="s">
         <v>145</v>
       </c>
@@ -18388,8 +19240,11 @@
       <c r="V283" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="284" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W283" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="284" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="8" t="s">
         <v>145</v>
       </c>
@@ -18446,8 +19301,11 @@
       <c r="V284" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="285" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W284" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="285" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="8" t="s">
         <v>145</v>
       </c>
@@ -18504,8 +19362,11 @@
       <c r="V285" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="286" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W285" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="286" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="8" t="s">
         <v>145</v>
       </c>
@@ -18562,8 +19423,11 @@
       <c r="V286" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="287" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W286" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="287" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="22" t="s">
         <v>146</v>
       </c>
@@ -18620,8 +19484,11 @@
       <c r="V287" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="288" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W287" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="288" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A288" s="22" t="s">
         <v>146</v>
       </c>
@@ -18678,8 +19545,11 @@
       <c r="V288" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="289" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W288" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A289" s="22" t="s">
         <v>146</v>
       </c>
@@ -18736,8 +19606,11 @@
       <c r="V289" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="290" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W289" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A290" s="22" t="s">
         <v>146</v>
       </c>
@@ -18794,8 +19667,11 @@
       <c r="V290" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="291" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W290" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="22" t="s">
         <v>146</v>
       </c>
@@ -18852,8 +19728,11 @@
       <c r="V291" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="292" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W291" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="22" t="s">
         <v>146</v>
       </c>
@@ -18910,8 +19789,11 @@
       <c r="V292" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="293" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W292" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293" s="8" t="s">
         <v>147</v>
       </c>
@@ -18968,8 +19850,11 @@
       <c r="V293" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="294" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W293" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294" s="8" t="s">
         <v>147</v>
       </c>
@@ -19026,8 +19911,11 @@
       <c r="V294" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="295" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W294" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="8" t="s">
         <v>147</v>
       </c>
@@ -19084,8 +19972,11 @@
       <c r="V295" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="296" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W295" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296" s="8" t="s">
         <v>147</v>
       </c>
@@ -19142,8 +20033,11 @@
       <c r="V296" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="297" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W296" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A297" s="22" t="s">
         <v>148</v>
       </c>
@@ -19198,8 +20092,11 @@
       <c r="V297" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="298" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W297" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="22" t="s">
         <v>148</v>
       </c>
@@ -19254,8 +20151,11 @@
       <c r="V298" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="299" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W298" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="299" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299" s="22" t="s">
         <v>148</v>
       </c>
@@ -19310,8 +20210,11 @@
       <c r="V299" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="300" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W299" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300" s="22" t="s">
         <v>148</v>
       </c>
@@ -19366,8 +20269,11 @@
       <c r="V300" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="301" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W300" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A301" s="22" t="s">
         <v>148</v>
       </c>
@@ -19422,8 +20328,11 @@
       <c r="V301" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="302" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W301" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="302" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302" s="22" t="s">
         <v>148</v>
       </c>
@@ -19478,8 +20387,11 @@
       <c r="V302" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="303" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W302" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="303" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303" s="22" t="s">
         <v>148</v>
       </c>
@@ -19534,8 +20446,11 @@
       <c r="V303" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="304" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W303" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="304" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304" s="8" t="s">
         <v>149</v>
       </c>
@@ -19592,8 +20507,11 @@
       <c r="V304" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="305" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W304" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="305" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305" s="8" t="s">
         <v>149</v>
       </c>
@@ -19650,8 +20568,11 @@
       <c r="V305" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="306" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W305" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="8" t="s">
         <v>149</v>
       </c>
@@ -19708,8 +20629,11 @@
       <c r="V306" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="307" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W306" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="307" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307" s="8" t="s">
         <v>149</v>
       </c>
@@ -19766,8 +20690,11 @@
       <c r="V307" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="308" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W307" s="89" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="308" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308" s="22" t="s">
         <v>150</v>
       </c>
@@ -19822,8 +20749,11 @@
       <c r="V308" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="309" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W308" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="309" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309" s="22" t="s">
         <v>150</v>
       </c>
@@ -19878,8 +20808,11 @@
       <c r="V309" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="310" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W309" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="310" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="22" t="s">
         <v>150</v>
       </c>
@@ -19934,8 +20867,11 @@
       <c r="V310" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="311" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W310" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="311" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="22" t="s">
         <v>150</v>
       </c>
@@ -19990,8 +20926,11 @@
       <c r="V311" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="312" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W311" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="312" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="22" t="s">
         <v>150</v>
       </c>
@@ -20046,8 +20985,11 @@
       <c r="V312" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="313" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W312" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="313" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313" s="22" t="s">
         <v>150</v>
       </c>
@@ -20102,8 +21044,11 @@
       <c r="V313" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="314" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W313" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="314" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314" s="22" t="s">
         <v>150</v>
       </c>
@@ -20158,8 +21103,11 @@
       <c r="V314" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="315" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W314" s="90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="315" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="8" t="s">
         <v>151</v>
       </c>
@@ -20214,8 +21162,11 @@
       <c r="V315" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="316" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W315" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="316" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="8" t="s">
         <v>151</v>
       </c>
@@ -20270,8 +21221,11 @@
       <c r="V316" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="317" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W316" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="317" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="8" t="s">
         <v>151</v>
       </c>
@@ -20326,8 +21280,11 @@
       <c r="V317" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="318" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W317" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="318" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="8" t="s">
         <v>151</v>
       </c>
@@ -20382,8 +21339,11 @@
       <c r="V318" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="319" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W318" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="319" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="8" t="s">
         <v>151</v>
       </c>
@@ -20438,8 +21398,11 @@
       <c r="V319" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="320" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W319" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="320" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="8" t="s">
         <v>151</v>
       </c>
@@ -20494,8 +21457,11 @@
       <c r="V320" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="321" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W320" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="321" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321" s="8" t="s">
         <v>151</v>
       </c>
@@ -20550,8 +21516,11 @@
       <c r="V321" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="322" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W321" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="322" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A322" s="8" t="s">
         <v>151</v>
       </c>
@@ -20606,8 +21575,11 @@
       <c r="V322" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="323" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W322" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="323" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A323" s="8" t="s">
         <v>151</v>
       </c>
@@ -20662,8 +21634,11 @@
       <c r="V323" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="324" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W323" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="324" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324" s="8" t="s">
         <v>151</v>
       </c>
@@ -20718,8 +21693,11 @@
       <c r="V324" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="325" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W324" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="325" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="8" t="s">
         <v>151</v>
       </c>
@@ -20774,8 +21752,11 @@
       <c r="V325" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="326" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W325" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="326" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="8" t="s">
         <v>151</v>
       </c>
@@ -20830,8 +21811,11 @@
       <c r="V326" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="327" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W326" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="327" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="8" t="s">
         <v>151</v>
       </c>
@@ -20886,8 +21870,11 @@
       <c r="V327" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="328" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W327" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="328" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328" s="8" t="s">
         <v>151</v>
       </c>
@@ -20942,8 +21929,11 @@
       <c r="V328" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="329" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W328" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="329" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="8" t="s">
         <v>151</v>
       </c>
@@ -20998,8 +21988,11 @@
       <c r="V329" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="330" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W329" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="330" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="8" t="s">
         <v>151</v>
       </c>
@@ -21054,8 +22047,11 @@
       <c r="V330" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="331" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W330" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="331" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331" s="8" t="s">
         <v>151</v>
       </c>
@@ -21110,8 +22106,11 @@
       <c r="V331" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="332" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W331" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="332" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332" s="8" t="s">
         <v>151</v>
       </c>
@@ -21166,8 +22165,11 @@
       <c r="V332" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="333" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W332" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="333" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A333" s="8" t="s">
         <v>151</v>
       </c>
@@ -21222,8 +22224,11 @@
       <c r="V333" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="334" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W333" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="334" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A334" s="8" t="s">
         <v>151</v>
       </c>
@@ -21278,8 +22283,11 @@
       <c r="V334" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="335" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W334" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="335" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A335" s="22" t="s">
         <v>152</v>
       </c>
@@ -21336,8 +22344,11 @@
       <c r="V335" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="336" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W335" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="336" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A336" s="22" t="s">
         <v>152</v>
       </c>
@@ -21394,8 +22405,11 @@
       <c r="V336" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="337" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W336" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="337" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A337" s="22" t="s">
         <v>152</v>
       </c>
@@ -21452,8 +22466,11 @@
       <c r="V337" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="338" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W337" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="338" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A338" s="22" t="s">
         <v>152</v>
       </c>
@@ -21510,8 +22527,11 @@
       <c r="V338" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="339" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W338" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="339" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A339" s="22" t="s">
         <v>152</v>
       </c>
@@ -21568,8 +22588,11 @@
       <c r="V339" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="340" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W339" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="340" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="8" t="s">
         <v>202</v>
       </c>
@@ -21626,8 +22649,11 @@
       <c r="V340" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="341" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W340" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="341" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A341" s="8" t="s">
         <v>202</v>
       </c>
@@ -21684,8 +22710,11 @@
       <c r="V341" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="342" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W341" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="342" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A342" s="8" t="s">
         <v>202</v>
       </c>
@@ -21742,8 +22771,11 @@
       <c r="V342" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="343" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W342" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="343" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A343" s="8" t="s">
         <v>202</v>
       </c>
@@ -21800,8 +22832,11 @@
       <c r="V343" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="344" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W343" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="344" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A344" s="8" t="s">
         <v>202</v>
       </c>
@@ -21858,8 +22893,11 @@
       <c r="V344" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="345" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W344" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="345" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A345" s="22" t="s">
         <v>203</v>
       </c>
@@ -21916,8 +22954,11 @@
       <c r="V345" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="346" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W345" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="346" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A346" s="22" t="s">
         <v>203</v>
       </c>
@@ -21974,8 +23015,11 @@
       <c r="V346" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="347" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W346" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="347" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A347" s="22" t="s">
         <v>203</v>
       </c>
@@ -22032,8 +23076,11 @@
       <c r="V347" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="348" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W347" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="348" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A348" s="22" t="s">
         <v>203</v>
       </c>
@@ -22090,8 +23137,11 @@
       <c r="V348" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="349" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W348" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="349" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A349" s="22" t="s">
         <v>203</v>
       </c>
@@ -22148,8 +23198,11 @@
       <c r="V349" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="350" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W349" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="350" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A350" s="8" t="s">
         <v>155</v>
       </c>
@@ -22206,8 +23259,11 @@
       <c r="V350" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="351" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W350" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="351" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A351" s="8" t="s">
         <v>155</v>
       </c>
@@ -22264,8 +23320,11 @@
       <c r="V351" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="352" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W351" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="352" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A352" s="8" t="s">
         <v>155</v>
       </c>
@@ -22322,8 +23381,11 @@
       <c r="V352" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="353" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W352" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="353" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A353" s="8" t="s">
         <v>155</v>
       </c>
@@ -22380,8 +23442,11 @@
       <c r="V353" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="354" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W353" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="354" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="8" t="s">
         <v>155</v>
       </c>
@@ -22438,8 +23503,11 @@
       <c r="V354" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="355" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W354" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="355" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355" s="22" t="s">
         <v>157</v>
       </c>
@@ -22496,8 +23564,11 @@
       <c r="V355" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="356" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W355" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="356" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356" s="22" t="s">
         <v>157</v>
       </c>
@@ -22554,8 +23625,11 @@
       <c r="V356" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="357" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W356" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="357" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357" s="22" t="s">
         <v>157</v>
       </c>
@@ -22612,8 +23686,11 @@
       <c r="V357" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="358" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W357" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="358" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358" s="22" t="s">
         <v>157</v>
       </c>
@@ -22670,8 +23747,11 @@
       <c r="V358" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="359" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W358" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="359" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359" s="22" t="s">
         <v>157</v>
       </c>
@@ -22728,8 +23808,11 @@
       <c r="V359" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="360" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W359" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="360" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360" s="22" t="s">
         <v>157</v>
       </c>
@@ -22786,8 +23869,11 @@
       <c r="V360" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="361" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W360" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="361" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361" s="22" t="s">
         <v>157</v>
       </c>
@@ -22844,8 +23930,11 @@
       <c r="V361" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="362" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W361" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="362" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362" s="22" t="s">
         <v>157</v>
       </c>
@@ -22902,8 +23991,11 @@
       <c r="V362" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="363" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W362" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="363" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363" s="22" t="s">
         <v>157</v>
       </c>
@@ -22960,8 +24052,11 @@
       <c r="V363" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="364" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W363" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="364" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364" s="56" t="s">
         <v>162</v>
       </c>
@@ -23016,8 +24111,11 @@
       <c r="V364" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="365" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W364" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="365" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365" s="56" t="s">
         <v>162</v>
       </c>
@@ -23072,8 +24170,11 @@
       <c r="V365" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="366" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W365" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="366" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A366" s="56" t="s">
         <v>162</v>
       </c>
@@ -23128,8 +24229,11 @@
       <c r="V366" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="367" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W366" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="367" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A367" s="56" t="s">
         <v>162</v>
       </c>
@@ -23184,8 +24288,11 @@
       <c r="V367" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="368" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W367" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="368" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368" s="56" t="s">
         <v>162</v>
       </c>
@@ -23240,8 +24347,11 @@
       <c r="V368" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="369" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W368" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="369" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369" s="56" t="s">
         <v>162</v>
       </c>
@@ -23296,8 +24406,11 @@
       <c r="V369" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="370" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W369" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="370" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370" s="22" t="s">
         <v>169</v>
       </c>
@@ -23354,8 +24467,11 @@
       <c r="V370" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="371" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W370" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="371" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371" s="22" t="s">
         <v>169</v>
       </c>
@@ -23412,8 +24528,11 @@
       <c r="V371" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="372" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W371" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="372" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A372" s="22" t="s">
         <v>169</v>
       </c>
@@ -23470,8 +24589,11 @@
       <c r="V372" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="373" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W372" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="373" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373" s="22" t="s">
         <v>169</v>
       </c>
@@ -23528,8 +24650,11 @@
       <c r="V373" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="374" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W373" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="374" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374" s="22" t="s">
         <v>169</v>
       </c>
@@ -23586,8 +24711,11 @@
       <c r="V374" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="375" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W374" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="375" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375" s="22" t="s">
         <v>169</v>
       </c>
@@ -23644,8 +24772,11 @@
       <c r="V375" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="376" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W375" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="376" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376" s="8" t="s">
         <v>175</v>
       </c>
@@ -23702,8 +24833,11 @@
       <c r="V376" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="377" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W376" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="377" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377" s="8" t="s">
         <v>175</v>
       </c>
@@ -23760,8 +24894,11 @@
       <c r="V377" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="378" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W377" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="378" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378" s="8" t="s">
         <v>175</v>
       </c>
@@ -23818,8 +24955,11 @@
       <c r="V378" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="379" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W378" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="379" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379" s="8" t="s">
         <v>175</v>
       </c>
@@ -23876,8 +25016,11 @@
       <c r="V379" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="380" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W379" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="380" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380" s="8" t="s">
         <v>175</v>
       </c>
@@ -23934,8 +25077,11 @@
       <c r="V380" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="381" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W380" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="381" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381" s="8" t="s">
         <v>175</v>
       </c>
@@ -23992,8 +25138,11 @@
       <c r="V381" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="382" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W381" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="382" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="8" t="s">
         <v>175</v>
       </c>
@@ -24050,8 +25199,11 @@
       <c r="V382" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="383" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W382" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="383" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383" s="8" t="s">
         <v>175</v>
       </c>
@@ -24108,8 +25260,11 @@
       <c r="V383" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="384" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W383" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="384" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384" s="8" t="s">
         <v>175</v>
       </c>
@@ -24166,8 +25321,11 @@
       <c r="V384" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="385" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W384" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="385" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385" s="8" t="s">
         <v>175</v>
       </c>
@@ -24224,8 +25382,11 @@
       <c r="V385" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="386" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W385" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="386" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386" s="8" t="s">
         <v>175</v>
       </c>
@@ -24282,8 +25443,11 @@
       <c r="V386" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="387" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W386" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="387" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387" s="8" t="s">
         <v>175</v>
       </c>
@@ -24340,8 +25504,11 @@
       <c r="V387" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="388" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W387" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="388" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388" s="8" t="s">
         <v>175</v>
       </c>
@@ -24398,8 +25565,11 @@
       <c r="V388" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="389" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W388" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="389" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389" s="8" t="s">
         <v>175</v>
       </c>
@@ -24456,8 +25626,11 @@
       <c r="V389" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="390" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W389" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="390" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390" s="8" t="s">
         <v>175</v>
       </c>
@@ -24514,8 +25687,11 @@
       <c r="V390" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="391" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W390" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="391" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391" s="8" t="s">
         <v>175</v>
       </c>
@@ -24572,8 +25748,11 @@
       <c r="V391" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="392" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W391" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="392" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392" s="8" t="s">
         <v>175</v>
       </c>
@@ -24630,8 +25809,11 @@
       <c r="V392" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="393" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W392" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="393" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393" s="8" t="s">
         <v>175</v>
       </c>
@@ -24688,8 +25870,11 @@
       <c r="V393" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="394" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W393" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="394" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394" s="8" t="s">
         <v>175</v>
       </c>
@@ -24746,8 +25931,11 @@
       <c r="V394" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="395" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W394" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="395" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395" s="8" t="s">
         <v>175</v>
       </c>
@@ -24804,8 +25992,11 @@
       <c r="V395" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="396" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W395" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="396" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="8" t="s">
         <v>175</v>
       </c>
@@ -24862,8 +26053,11 @@
       <c r="V396" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="397" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W396" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="397" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397" s="8" t="s">
         <v>175</v>
       </c>
@@ -24920,8 +26114,11 @@
       <c r="V397" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="398" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W397" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="398" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398" s="8" t="s">
         <v>175</v>
       </c>
@@ -24978,8 +26175,11 @@
       <c r="V398" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="399" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W398" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="399" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A399" s="8" t="s">
         <v>175</v>
       </c>
@@ -25036,8 +26236,11 @@
       <c r="V399" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="400" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W399" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="400" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A400" s="8" t="s">
         <v>175</v>
       </c>
@@ -25094,8 +26297,11 @@
       <c r="V400" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="401" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W400" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="401" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A401" s="8" t="s">
         <v>175</v>
       </c>
@@ -25152,8 +26358,11 @@
       <c r="V401" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="402" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W401" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="402" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402" s="8" t="s">
         <v>175</v>
       </c>
@@ -25210,8 +26419,11 @@
       <c r="V402" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="403" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W402" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="403" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403" s="8" t="s">
         <v>175</v>
       </c>
@@ -25268,8 +26480,11 @@
       <c r="V403" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="404" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W403" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="404" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404" s="8" t="s">
         <v>175</v>
       </c>
@@ -25326,8 +26541,11 @@
       <c r="V404" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="405" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W404" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="405" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405" s="8" t="s">
         <v>175</v>
       </c>
@@ -25384,8 +26602,11 @@
       <c r="V405" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="406" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W405" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="406" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406" s="8" t="s">
         <v>175</v>
       </c>
@@ -25442,8 +26663,11 @@
       <c r="V406" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="407" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W406" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="407" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407" s="8" t="s">
         <v>175</v>
       </c>
@@ -25500,8 +26724,11 @@
       <c r="V407" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="408" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W407" s="89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="408" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408" s="61" t="s">
         <v>178</v>
       </c>
@@ -25558,8 +26785,11 @@
       <c r="V408" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="409" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W408" s="55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="409" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409" s="61" t="s">
         <v>178</v>
       </c>
@@ -25616,8 +26846,11 @@
       <c r="V409" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="410" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W409" s="55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="410" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="61" t="s">
         <v>178</v>
       </c>
@@ -25674,8 +26907,11 @@
       <c r="V410" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="411" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W410" s="55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="411" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411" s="61" t="s">
         <v>178</v>
       </c>
@@ -25732,8 +26968,11 @@
       <c r="V411" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="412" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W411" s="55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="412" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412" s="56" t="s">
         <v>198</v>
       </c>
@@ -25792,8 +27031,11 @@
       <c r="V412" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="413" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W412" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="413" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413" s="56" t="s">
         <v>198</v>
       </c>
@@ -25852,8 +27094,11 @@
       <c r="V413" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="414" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W413" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="414" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414" s="56" t="s">
         <v>198</v>
       </c>
@@ -25912,8 +27157,11 @@
       <c r="V414" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="415" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W414" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="415" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415" s="56" t="s">
         <v>198</v>
       </c>
@@ -25972,8 +27220,11 @@
       <c r="V415" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="416" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W415" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="416" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416" s="56" t="s">
         <v>198</v>
       </c>
@@ -26032,8 +27283,11 @@
       <c r="V416" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="417" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W416" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="417" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417" s="56" t="s">
         <v>198</v>
       </c>
@@ -26092,8 +27346,11 @@
       <c r="V417" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="418" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W417" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="418" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418" s="56" t="s">
         <v>198</v>
       </c>
@@ -26152,8 +27409,11 @@
       <c r="V418" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="419" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W418" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="419" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419" s="56" t="s">
         <v>198</v>
       </c>
@@ -26212,8 +27472,11 @@
       <c r="V419" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="420" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W419" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="420" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420" s="64" t="s">
         <v>199</v>
       </c>
@@ -26272,8 +27535,11 @@
       <c r="V420" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="421" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W420" s="55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="421" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421" s="64" t="s">
         <v>199</v>
       </c>
@@ -26332,8 +27598,11 @@
       <c r="V421" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="422" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W421" s="55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="422" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422" s="64" t="s">
         <v>199</v>
       </c>
@@ -26392,8 +27661,11 @@
       <c r="V422" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="423" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W422" s="55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="423" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423" s="64" t="s">
         <v>199</v>
       </c>
@@ -26452,8 +27724,11 @@
       <c r="V423" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="424" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W423" s="55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="424" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="64" t="s">
         <v>199</v>
       </c>
@@ -26512,8 +27787,11 @@
       <c r="V424" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="425" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W424" s="55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="425" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425" s="64" t="s">
         <v>199</v>
       </c>
@@ -26572,8 +27850,11 @@
       <c r="V425" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="426" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W425" s="55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="426" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A426" s="64" t="s">
         <v>199</v>
       </c>
@@ -26632,8 +27913,11 @@
       <c r="V426" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="427" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W426" s="55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="427" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427" s="64" t="s">
         <v>199</v>
       </c>
@@ -26692,8 +27976,11 @@
       <c r="V427" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="428" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W427" s="55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="428" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428" s="56" t="s">
         <v>200</v>
       </c>
@@ -26752,8 +28039,11 @@
       <c r="V428" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="429" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W428" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="429" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429" s="56" t="s">
         <v>200</v>
       </c>
@@ -26812,8 +28102,11 @@
       <c r="V429" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="430" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W429" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="430" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430" s="56" t="s">
         <v>200</v>
       </c>
@@ -26872,8 +28165,11 @@
       <c r="V430" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="431" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W430" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="431" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431" s="56" t="s">
         <v>200</v>
       </c>
@@ -26932,8 +28228,11 @@
       <c r="V431" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="432" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W431" s="48" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="432" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432" s="56" t="s">
         <v>200</v>
       </c>
@@ -26992,6 +28291,9 @@
       <c r="V432" s="10" t="s">
         <v>197</v>
       </c>
+      <c r="W432" s="48" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="433" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="56" t="s">
@@ -27052,6 +28354,9 @@
       <c r="V433" s="10" t="s">
         <v>197</v>
       </c>
+      <c r="W433" s="48" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="434" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="56" t="s">
@@ -27112,6 +28417,9 @@
       <c r="V434" s="10" t="s">
         <v>197</v>
       </c>
+      <c r="W434" s="48" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="435" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="56" t="s">
@@ -27172,6 +28480,9 @@
       <c r="V435" s="10" t="s">
         <v>197</v>
       </c>
+      <c r="W435" s="48" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="436" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="64" t="s">
@@ -27232,6 +28543,9 @@
       <c r="V436" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W436" s="55" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="437" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="64" t="s">
@@ -27292,6 +28606,9 @@
       <c r="V437" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W437" s="55" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="438" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="64" t="s">
@@ -27352,6 +28669,9 @@
       <c r="V438" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W438" s="55" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="439" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="64" t="s">
@@ -27412,6 +28732,9 @@
       <c r="V439" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W439" s="55" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="440" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="64" t="s">
@@ -27472,6 +28795,9 @@
       <c r="V440" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W440" s="55" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="441" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="64" t="s">
@@ -27532,6 +28858,9 @@
       <c r="V441" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W441" s="55" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="442" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="64" t="s">
@@ -27592,6 +28921,9 @@
       <c r="V442" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W442" s="55" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="443" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443" s="64" t="s">
@@ -27651,6 +28983,9 @@
       </c>
       <c r="V443" s="24" t="s">
         <v>197</v>
+      </c>
+      <c r="W443" s="55" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="444" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27712,7 +29047,9 @@
       <c r="V444" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W444" s="14"/>
+      <c r="W444" s="31" t="s">
+        <v>224</v>
+      </c>
       <c r="X444" s="20"/>
       <c r="Y444" s="20"/>
       <c r="Z444" s="20"/>
@@ -27791,7 +29128,9 @@
       <c r="V445" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W445" s="14"/>
+      <c r="W445" s="31" t="s">
+        <v>224</v>
+      </c>
       <c r="X445" s="20"/>
       <c r="Y445" s="20"/>
       <c r="Z445" s="20"/>
@@ -27870,7 +29209,9 @@
       <c r="V446" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W446" s="14"/>
+      <c r="W446" s="31" t="s">
+        <v>224</v>
+      </c>
       <c r="X446" s="20"/>
       <c r="Y446" s="20"/>
       <c r="Z446" s="20"/>
@@ -27949,7 +29290,9 @@
       <c r="V447" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W447" s="14"/>
+      <c r="W447" s="31" t="s">
+        <v>224</v>
+      </c>
       <c r="X447" s="20"/>
       <c r="Y447" s="20"/>
       <c r="Z447" s="20"/>
@@ -28028,7 +29371,9 @@
       <c r="V448" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W448" s="14"/>
+      <c r="W448" s="31" t="s">
+        <v>224</v>
+      </c>
       <c r="X448" s="20"/>
       <c r="Y448" s="20"/>
       <c r="Z448" s="20"/>
@@ -28107,7 +29452,9 @@
       <c r="V449" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W449" s="14"/>
+      <c r="W449" s="31" t="s">
+        <v>224</v>
+      </c>
       <c r="X449" s="20"/>
       <c r="Y449" s="20"/>
       <c r="Z449" s="20"/>
@@ -28186,7 +29533,9 @@
       <c r="V450" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W450" s="14"/>
+      <c r="W450" s="31" t="s">
+        <v>224</v>
+      </c>
       <c r="X450" s="20"/>
       <c r="Y450" s="20"/>
       <c r="Z450" s="20"/>
@@ -28265,7 +29614,9 @@
       <c r="V451" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W451" s="14"/>
+      <c r="W451" s="31" t="s">
+        <v>224</v>
+      </c>
       <c r="X451" s="20"/>
       <c r="Y451" s="20"/>
       <c r="Z451" s="20"/>
@@ -28344,7 +29695,9 @@
       <c r="V452" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W452" s="27"/>
+      <c r="W452" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X452" s="28"/>
       <c r="Y452" s="28"/>
       <c r="Z452" s="28"/>
@@ -28423,7 +29776,9 @@
       <c r="V453" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W453" s="27"/>
+      <c r="W453" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X453" s="28"/>
       <c r="Y453" s="28"/>
       <c r="Z453" s="28"/>
@@ -28502,7 +29857,9 @@
       <c r="V454" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W454" s="27"/>
+      <c r="W454" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X454" s="28"/>
       <c r="Y454" s="28"/>
       <c r="Z454" s="28"/>
@@ -28581,7 +29938,9 @@
       <c r="V455" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W455" s="27"/>
+      <c r="W455" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X455" s="28"/>
       <c r="Y455" s="28"/>
       <c r="Z455" s="28"/>
@@ -28660,7 +30019,9 @@
       <c r="V456" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W456" s="27"/>
+      <c r="W456" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X456" s="28"/>
       <c r="Y456" s="28"/>
       <c r="Z456" s="28"/>
@@ -28739,7 +30100,9 @@
       <c r="V457" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W457" s="27"/>
+      <c r="W457" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X457" s="28"/>
       <c r="Y457" s="28"/>
       <c r="Z457" s="28"/>
@@ -28818,7 +30181,9 @@
       <c r="V458" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W458" s="27"/>
+      <c r="W458" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X458" s="28"/>
       <c r="Y458" s="28"/>
       <c r="Z458" s="28"/>
@@ -28897,7 +30262,9 @@
       <c r="V459" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W459" s="27"/>
+      <c r="W459" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X459" s="28"/>
       <c r="Y459" s="28"/>
       <c r="Z459" s="28"/>
@@ -28976,7 +30343,9 @@
       <c r="V460" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W460" s="27"/>
+      <c r="W460" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X460" s="28"/>
       <c r="Y460" s="28"/>
       <c r="Z460" s="28"/>
@@ -29055,7 +30424,9 @@
       <c r="V461" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W461" s="27"/>
+      <c r="W461" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X461" s="28"/>
       <c r="Y461" s="28"/>
       <c r="Z461" s="28"/>
@@ -29134,7 +30505,9 @@
       <c r="V462" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W462" s="27"/>
+      <c r="W462" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X462" s="28"/>
       <c r="Y462" s="28"/>
       <c r="Z462" s="28"/>
@@ -29213,7 +30586,9 @@
       <c r="V463" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W463" s="27"/>
+      <c r="W463" s="55" t="s">
+        <v>224</v>
+      </c>
       <c r="X463" s="28"/>
       <c r="Y463" s="28"/>
       <c r="Z463" s="28"/>
@@ -29292,7 +30667,9 @@
       <c r="V464" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W464" s="20"/>
+      <c r="W464" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X464" s="20"/>
       <c r="Y464" s="20"/>
       <c r="Z464" s="20"/>
@@ -29308,12 +30685,8 @@
       <c r="AJ464" s="14"/>
       <c r="AK464" s="14"/>
       <c r="AL464" s="14"/>
-      <c r="AM464" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN464" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM464" s="40"/>
+      <c r="AN464" s="40"/>
     </row>
     <row r="465" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465" s="56" t="s">
@@ -29374,7 +30747,9 @@
       <c r="V465" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W465" s="20"/>
+      <c r="W465" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X465" s="20"/>
       <c r="Y465" s="20"/>
       <c r="Z465" s="20"/>
@@ -29390,12 +30765,8 @@
       <c r="AJ465" s="14"/>
       <c r="AK465" s="14"/>
       <c r="AL465" s="14"/>
-      <c r="AM465" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN465" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM465" s="40"/>
+      <c r="AN465" s="40"/>
     </row>
     <row r="466" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="56" t="s">
@@ -29456,7 +30827,9 @@
       <c r="V466" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W466" s="20"/>
+      <c r="W466" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X466" s="20"/>
       <c r="Y466" s="20"/>
       <c r="Z466" s="20"/>
@@ -29472,12 +30845,8 @@
       <c r="AJ466" s="14"/>
       <c r="AK466" s="14"/>
       <c r="AL466" s="14"/>
-      <c r="AM466" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN466" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM466" s="40"/>
+      <c r="AN466" s="40"/>
     </row>
     <row r="467" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467" s="56" t="s">
@@ -29538,7 +30907,9 @@
       <c r="V467" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W467" s="20"/>
+      <c r="W467" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X467" s="20"/>
       <c r="Y467" s="20"/>
       <c r="Z467" s="20"/>
@@ -29554,12 +30925,8 @@
       <c r="AJ467" s="14"/>
       <c r="AK467" s="14"/>
       <c r="AL467" s="14"/>
-      <c r="AM467" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN467" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM467" s="40"/>
+      <c r="AN467" s="40"/>
     </row>
     <row r="468" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468" s="56" t="s">
@@ -29620,7 +30987,9 @@
       <c r="V468" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W468" s="20"/>
+      <c r="W468" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X468" s="20"/>
       <c r="Y468" s="20"/>
       <c r="Z468" s="20"/>
@@ -29636,12 +31005,8 @@
       <c r="AJ468" s="14"/>
       <c r="AK468" s="14"/>
       <c r="AL468" s="14"/>
-      <c r="AM468" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN468" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM468" s="40"/>
+      <c r="AN468" s="40"/>
     </row>
     <row r="469" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A469" s="56" t="s">
@@ -29702,7 +31067,9 @@
       <c r="V469" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W469" s="20"/>
+      <c r="W469" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X469" s="20"/>
       <c r="Y469" s="20"/>
       <c r="Z469" s="20"/>
@@ -29718,12 +31085,8 @@
       <c r="AJ469" s="14"/>
       <c r="AK469" s="14"/>
       <c r="AL469" s="14"/>
-      <c r="AM469" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN469" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM469" s="40"/>
+      <c r="AN469" s="40"/>
     </row>
     <row r="470" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470" s="56" t="s">
@@ -29784,7 +31147,9 @@
       <c r="V470" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W470" s="20"/>
+      <c r="W470" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X470" s="20"/>
       <c r="Y470" s="20"/>
       <c r="Z470" s="20"/>
@@ -29800,12 +31165,8 @@
       <c r="AJ470" s="14"/>
       <c r="AK470" s="14"/>
       <c r="AL470" s="14"/>
-      <c r="AM470" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN470" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM470" s="40"/>
+      <c r="AN470" s="40"/>
     </row>
     <row r="471" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471" s="56" t="s">
@@ -29866,7 +31227,9 @@
       <c r="V471" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W471" s="20"/>
+      <c r="W471" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X471" s="20"/>
       <c r="Y471" s="20"/>
       <c r="Z471" s="20"/>
@@ -29882,12 +31245,8 @@
       <c r="AJ471" s="14"/>
       <c r="AK471" s="14"/>
       <c r="AL471" s="14"/>
-      <c r="AM471" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN471" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM471" s="40"/>
+      <c r="AN471" s="40"/>
     </row>
     <row r="472" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472" s="56" t="s">
@@ -29948,7 +31307,9 @@
       <c r="V472" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W472" s="20"/>
+      <c r="W472" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X472" s="20"/>
       <c r="Y472" s="20"/>
       <c r="Z472" s="20"/>
@@ -29964,16 +31325,12 @@
       <c r="AJ472" s="14"/>
       <c r="AK472" s="14"/>
       <c r="AL472" s="14"/>
-      <c r="AM472" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN472" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM472" s="40"/>
+      <c r="AN472" s="40"/>
     </row>
     <row r="473" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B473" s="39" t="s">
         <v>215</v>
@@ -29995,7 +31352,7 @@
         <v>208</v>
       </c>
       <c r="I473" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J473" s="41"/>
       <c r="K473" s="59">
@@ -30030,7 +31387,9 @@
       <c r="V473" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W473" s="20"/>
+      <c r="W473" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X473" s="20"/>
       <c r="Y473" s="20"/>
       <c r="Z473" s="20"/>
@@ -30046,16 +31405,12 @@
       <c r="AJ473" s="14"/>
       <c r="AK473" s="14"/>
       <c r="AL473" s="14"/>
-      <c r="AM473" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN473" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM473" s="40"/>
+      <c r="AN473" s="40"/>
     </row>
     <row r="474" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B474" s="39" t="s">
         <v>215</v>
@@ -30077,7 +31432,7 @@
         <v>208</v>
       </c>
       <c r="I474" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J474" s="41"/>
       <c r="K474" s="59">
@@ -30112,7 +31467,9 @@
       <c r="V474" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W474" s="20"/>
+      <c r="W474" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X474" s="20"/>
       <c r="Y474" s="20"/>
       <c r="Z474" s="20"/>
@@ -30128,16 +31485,12 @@
       <c r="AJ474" s="14"/>
       <c r="AK474" s="14"/>
       <c r="AL474" s="14"/>
-      <c r="AM474" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN474" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM474" s="40"/>
+      <c r="AN474" s="40"/>
     </row>
     <row r="475" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B475" s="39" t="s">
         <v>215</v>
@@ -30159,7 +31512,7 @@
         <v>208</v>
       </c>
       <c r="I475" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J475" s="41"/>
       <c r="K475" s="59">
@@ -30194,7 +31547,9 @@
       <c r="V475" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W475" s="20"/>
+      <c r="W475" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X475" s="20"/>
       <c r="Y475" s="20"/>
       <c r="Z475" s="20"/>
@@ -30210,16 +31565,12 @@
       <c r="AJ475" s="14"/>
       <c r="AK475" s="14"/>
       <c r="AL475" s="14"/>
-      <c r="AM475" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN475" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM475" s="40"/>
+      <c r="AN475" s="40"/>
     </row>
     <row r="476" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A476" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B476" s="39" t="s">
         <v>215</v>
@@ -30241,7 +31592,7 @@
         <v>208</v>
       </c>
       <c r="I476" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J476" s="41"/>
       <c r="K476" s="59">
@@ -30276,7 +31627,9 @@
       <c r="V476" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W476" s="20"/>
+      <c r="W476" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X476" s="20"/>
       <c r="Y476" s="20"/>
       <c r="Z476" s="20"/>
@@ -30292,16 +31645,12 @@
       <c r="AJ476" s="14"/>
       <c r="AK476" s="14"/>
       <c r="AL476" s="14"/>
-      <c r="AM476" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN476" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM476" s="40"/>
+      <c r="AN476" s="40"/>
     </row>
     <row r="477" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A477" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B477" s="39" t="s">
         <v>215</v>
@@ -30323,7 +31672,7 @@
         <v>208</v>
       </c>
       <c r="I477" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J477" s="41"/>
       <c r="K477" s="59">
@@ -30358,7 +31707,9 @@
       <c r="V477" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W477" s="20"/>
+      <c r="W477" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X477" s="20"/>
       <c r="Y477" s="20"/>
       <c r="Z477" s="20"/>
@@ -30374,16 +31725,12 @@
       <c r="AJ477" s="14"/>
       <c r="AK477" s="14"/>
       <c r="AL477" s="14"/>
-      <c r="AM477" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN477" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM477" s="40"/>
+      <c r="AN477" s="40"/>
     </row>
     <row r="478" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A478" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B478" s="39" t="s">
         <v>215</v>
@@ -30405,7 +31752,7 @@
         <v>208</v>
       </c>
       <c r="I478" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J478" s="41"/>
       <c r="K478" s="59">
@@ -30440,7 +31787,9 @@
       <c r="V478" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W478" s="20"/>
+      <c r="W478" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X478" s="20"/>
       <c r="Y478" s="20"/>
       <c r="Z478" s="20"/>
@@ -30456,16 +31805,12 @@
       <c r="AJ478" s="14"/>
       <c r="AK478" s="14"/>
       <c r="AL478" s="14"/>
-      <c r="AM478" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN478" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM478" s="40"/>
+      <c r="AN478" s="40"/>
     </row>
     <row r="479" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A479" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B479" s="39" t="s">
         <v>215</v>
@@ -30487,7 +31832,7 @@
         <v>208</v>
       </c>
       <c r="I479" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J479" s="41"/>
       <c r="K479" s="59">
@@ -30522,7 +31867,9 @@
       <c r="V479" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W479" s="20"/>
+      <c r="W479" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X479" s="20"/>
       <c r="Y479" s="20"/>
       <c r="Z479" s="20"/>
@@ -30538,16 +31885,12 @@
       <c r="AJ479" s="14"/>
       <c r="AK479" s="14"/>
       <c r="AL479" s="14"/>
-      <c r="AM479" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN479" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM479" s="40"/>
+      <c r="AN479" s="40"/>
     </row>
     <row r="480" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B480" s="39" t="s">
         <v>215</v>
@@ -30569,7 +31912,7 @@
         <v>208</v>
       </c>
       <c r="I480" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J480" s="41"/>
       <c r="K480" s="59">
@@ -30604,7 +31947,9 @@
       <c r="V480" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W480" s="20"/>
+      <c r="W480" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X480" s="20"/>
       <c r="Y480" s="20"/>
       <c r="Z480" s="20"/>
@@ -30620,16 +31965,12 @@
       <c r="AJ480" s="14"/>
       <c r="AK480" s="14"/>
       <c r="AL480" s="14"/>
-      <c r="AM480" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN480" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM480" s="40"/>
+      <c r="AN480" s="40"/>
     </row>
     <row r="481" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A481" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B481" s="39" t="s">
         <v>215</v>
@@ -30651,7 +31992,7 @@
         <v>208</v>
       </c>
       <c r="I481" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J481" s="41"/>
       <c r="K481" s="59">
@@ -30686,7 +32027,9 @@
       <c r="V481" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W481" s="20"/>
+      <c r="W481" s="91" t="s">
+        <v>225</v>
+      </c>
       <c r="X481" s="20"/>
       <c r="Y481" s="20"/>
       <c r="Z481" s="20"/>
@@ -30702,972 +32045,8 @@
       <c r="AJ481" s="14"/>
       <c r="AK481" s="14"/>
       <c r="AL481" s="14"/>
-      <c r="AM481" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN481" s="40" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="482" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A482" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B482" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C482" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D482" s="50"/>
-      <c r="E482" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F482" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G482" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H482" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I482" s="63"/>
-      <c r="J482" s="52"/>
-      <c r="K482" s="54">
-        <v>1</v>
-      </c>
-      <c r="L482" s="88">
-        <v>35947</v>
-      </c>
-      <c r="M482" s="50"/>
-      <c r="N482" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O482" s="54">
-        <v>1</v>
-      </c>
-      <c r="P482" s="53"/>
-      <c r="Q482" s="54">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="R482" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S482" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T482" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U482" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V482" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W482" s="54"/>
-      <c r="X482" s="54"/>
-      <c r="Y482" s="54"/>
-      <c r="Z482" s="54"/>
-      <c r="AA482" s="52"/>
-      <c r="AB482" s="52"/>
-      <c r="AC482" s="52"/>
-      <c r="AD482" s="52"/>
-      <c r="AE482" s="52"/>
-      <c r="AF482" s="52"/>
-      <c r="AG482" s="52"/>
-      <c r="AH482" s="52"/>
-      <c r="AI482" s="52"/>
-      <c r="AJ482" s="52"/>
-      <c r="AK482" s="52"/>
-      <c r="AL482" s="52"/>
-      <c r="AM482" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN482" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="483" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A483" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B483" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C483" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D483" s="50"/>
-      <c r="E483" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F483" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G483" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H483" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I483" s="63"/>
-      <c r="J483" s="52"/>
-      <c r="K483" s="54">
-        <v>2</v>
-      </c>
-      <c r="L483" s="88">
-        <v>36069</v>
-      </c>
-      <c r="M483" s="52"/>
-      <c r="N483" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O483" s="54">
-        <v>1</v>
-      </c>
-      <c r="P483" s="53"/>
-      <c r="Q483" s="54">
-        <v>49.7</v>
-      </c>
-      <c r="R483" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S483" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T483" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U483" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V483" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W483" s="54"/>
-      <c r="X483" s="54"/>
-      <c r="Y483" s="54"/>
-      <c r="Z483" s="54"/>
-      <c r="AA483" s="52"/>
-      <c r="AB483" s="52"/>
-      <c r="AC483" s="52"/>
-      <c r="AD483" s="52"/>
-      <c r="AE483" s="52"/>
-      <c r="AF483" s="52"/>
-      <c r="AG483" s="52"/>
-      <c r="AH483" s="52"/>
-      <c r="AI483" s="52"/>
-      <c r="AJ483" s="52"/>
-      <c r="AK483" s="52"/>
-      <c r="AL483" s="52"/>
-      <c r="AM483" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN483" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="484" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A484" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B484" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C484" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D484" s="50"/>
-      <c r="E484" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F484" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G484" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H484" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I484" s="63"/>
-      <c r="J484" s="52"/>
-      <c r="K484" s="54">
-        <v>3</v>
-      </c>
-      <c r="L484" s="88">
-        <v>36161</v>
-      </c>
-      <c r="M484" s="52"/>
-      <c r="N484" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O484" s="54">
-        <v>1</v>
-      </c>
-      <c r="P484" s="53"/>
-      <c r="Q484" s="54">
-        <v>59.5</v>
-      </c>
-      <c r="R484" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S484" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T484" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U484" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V484" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W484" s="54"/>
-      <c r="X484" s="54"/>
-      <c r="Y484" s="54"/>
-      <c r="Z484" s="54"/>
-      <c r="AA484" s="52"/>
-      <c r="AB484" s="52"/>
-      <c r="AC484" s="52"/>
-      <c r="AD484" s="52"/>
-      <c r="AE484" s="52"/>
-      <c r="AF484" s="52"/>
-      <c r="AG484" s="52"/>
-      <c r="AH484" s="52"/>
-      <c r="AI484" s="52"/>
-      <c r="AJ484" s="52"/>
-      <c r="AK484" s="52"/>
-      <c r="AL484" s="52"/>
-      <c r="AM484" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN484" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="485" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A485" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B485" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C485" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D485" s="50"/>
-      <c r="E485" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F485" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G485" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H485" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I485" s="63"/>
-      <c r="J485" s="52"/>
-      <c r="K485" s="54">
-        <v>4</v>
-      </c>
-      <c r="L485" s="88">
-        <v>36281</v>
-      </c>
-      <c r="M485" s="52"/>
-      <c r="N485" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O485" s="53">
-        <v>0</v>
-      </c>
-      <c r="P485" s="53"/>
-      <c r="Q485" s="54">
-        <v>47.5</v>
-      </c>
-      <c r="R485" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S485" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T485" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U485" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V485" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W485" s="54"/>
-      <c r="X485" s="54"/>
-      <c r="Y485" s="54"/>
-      <c r="Z485" s="54"/>
-      <c r="AA485" s="52"/>
-      <c r="AB485" s="52"/>
-      <c r="AC485" s="52"/>
-      <c r="AD485" s="52"/>
-      <c r="AE485" s="52"/>
-      <c r="AF485" s="52"/>
-      <c r="AG485" s="52"/>
-      <c r="AH485" s="52"/>
-      <c r="AI485" s="52"/>
-      <c r="AJ485" s="52"/>
-      <c r="AK485" s="52"/>
-      <c r="AL485" s="52"/>
-      <c r="AM485" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN485" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="486" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A486" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B486" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C486" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D486" s="50"/>
-      <c r="E486" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F486" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G486" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H486" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I486" s="63"/>
-      <c r="J486" s="52"/>
-      <c r="K486" s="54">
-        <v>5</v>
-      </c>
-      <c r="L486" s="88">
-        <v>36342</v>
-      </c>
-      <c r="M486" s="52"/>
-      <c r="N486" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O486" s="53">
-        <v>0</v>
-      </c>
-      <c r="P486" s="53"/>
-      <c r="Q486" s="54">
-        <v>38</v>
-      </c>
-      <c r="R486" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S486" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T486" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U486" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V486" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W486" s="54"/>
-      <c r="X486" s="54"/>
-      <c r="Y486" s="54"/>
-      <c r="Z486" s="54"/>
-      <c r="AA486" s="52"/>
-      <c r="AB486" s="52"/>
-      <c r="AC486" s="52"/>
-      <c r="AD486" s="52"/>
-      <c r="AE486" s="52"/>
-      <c r="AF486" s="52"/>
-      <c r="AG486" s="52"/>
-      <c r="AH486" s="52"/>
-      <c r="AI486" s="52"/>
-      <c r="AJ486" s="52"/>
-      <c r="AK486" s="52"/>
-      <c r="AL486" s="52"/>
-      <c r="AM486" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN486" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="487" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A487" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B487" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C487" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D487" s="50"/>
-      <c r="E487" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F487" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G487" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H487" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I487" s="63"/>
-      <c r="J487" s="52"/>
-      <c r="K487" s="54">
-        <v>6</v>
-      </c>
-      <c r="L487" s="88">
-        <v>36404</v>
-      </c>
-      <c r="M487" s="52"/>
-      <c r="N487" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O487" s="53">
-        <v>0</v>
-      </c>
-      <c r="P487" s="53"/>
-      <c r="Q487" s="54">
-        <v>94.3</v>
-      </c>
-      <c r="R487" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S487" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T487" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U487" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V487" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W487" s="54"/>
-      <c r="X487" s="54"/>
-      <c r="Y487" s="54"/>
-      <c r="Z487" s="54"/>
-      <c r="AA487" s="52"/>
-      <c r="AB487" s="52"/>
-      <c r="AC487" s="52"/>
-      <c r="AD487" s="52"/>
-      <c r="AE487" s="52"/>
-      <c r="AF487" s="52"/>
-      <c r="AG487" s="52"/>
-      <c r="AH487" s="52"/>
-      <c r="AI487" s="52"/>
-      <c r="AJ487" s="52"/>
-      <c r="AK487" s="52"/>
-      <c r="AL487" s="52"/>
-      <c r="AM487" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN487" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="488" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A488" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B488" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C488" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D488" s="50"/>
-      <c r="E488" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F488" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G488" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H488" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I488" s="63"/>
-      <c r="J488" s="52"/>
-      <c r="K488" s="54">
-        <v>7</v>
-      </c>
-      <c r="L488" s="88">
-        <v>36495</v>
-      </c>
-      <c r="M488" s="52"/>
-      <c r="N488" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O488" s="53">
-        <v>0</v>
-      </c>
-      <c r="P488" s="53"/>
-      <c r="Q488" s="54">
-        <v>51.5</v>
-      </c>
-      <c r="R488" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S488" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T488" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U488" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V488" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W488" s="54"/>
-      <c r="X488" s="54"/>
-      <c r="Y488" s="54"/>
-      <c r="Z488" s="54"/>
-      <c r="AA488" s="52"/>
-      <c r="AB488" s="52"/>
-      <c r="AC488" s="52"/>
-      <c r="AD488" s="52"/>
-      <c r="AE488" s="52"/>
-      <c r="AF488" s="52"/>
-      <c r="AG488" s="52"/>
-      <c r="AH488" s="52"/>
-      <c r="AI488" s="52"/>
-      <c r="AJ488" s="52"/>
-      <c r="AK488" s="52"/>
-      <c r="AL488" s="52"/>
-      <c r="AM488" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN488" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="489" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A489" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B489" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C489" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D489" s="50"/>
-      <c r="E489" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F489" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G489" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H489" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I489" s="63"/>
-      <c r="J489" s="52"/>
-      <c r="K489" s="54">
-        <v>8</v>
-      </c>
-      <c r="L489" s="88">
-        <v>36557</v>
-      </c>
-      <c r="M489" s="52"/>
-      <c r="N489" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O489" s="53">
-        <v>0</v>
-      </c>
-      <c r="P489" s="53"/>
-      <c r="Q489" s="54">
-        <v>60.7</v>
-      </c>
-      <c r="R489" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S489" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T489" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U489" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V489" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W489" s="54"/>
-      <c r="X489" s="54"/>
-      <c r="Y489" s="54"/>
-      <c r="Z489" s="54"/>
-      <c r="AA489" s="52"/>
-      <c r="AB489" s="52"/>
-      <c r="AC489" s="52"/>
-      <c r="AD489" s="52"/>
-      <c r="AE489" s="52"/>
-      <c r="AF489" s="52"/>
-      <c r="AG489" s="52"/>
-      <c r="AH489" s="52"/>
-      <c r="AI489" s="52"/>
-      <c r="AJ489" s="52"/>
-      <c r="AK489" s="52"/>
-      <c r="AL489" s="52"/>
-      <c r="AM489" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN489" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="490" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A490" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B490" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C490" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D490" s="50"/>
-      <c r="E490" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F490" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G490" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H490" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I490" s="63"/>
-      <c r="J490" s="52"/>
-      <c r="K490" s="54">
-        <v>9</v>
-      </c>
-      <c r="L490" s="88">
-        <v>36770</v>
-      </c>
-      <c r="M490" s="52"/>
-      <c r="N490" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O490" s="53">
-        <v>0</v>
-      </c>
-      <c r="P490" s="53"/>
-      <c r="Q490" s="54">
-        <v>55.2</v>
-      </c>
-      <c r="R490" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S490" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T490" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U490" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V490" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W490" s="54"/>
-      <c r="X490" s="54"/>
-      <c r="Y490" s="54"/>
-      <c r="Z490" s="54"/>
-      <c r="AA490" s="52"/>
-      <c r="AB490" s="52"/>
-      <c r="AC490" s="52"/>
-      <c r="AD490" s="52"/>
-      <c r="AE490" s="52"/>
-      <c r="AF490" s="52"/>
-      <c r="AG490" s="52"/>
-      <c r="AH490" s="52"/>
-      <c r="AI490" s="52"/>
-      <c r="AJ490" s="52"/>
-      <c r="AK490" s="52"/>
-      <c r="AL490" s="52"/>
-      <c r="AM490" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN490" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="491" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A491" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B491" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C491" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D491" s="50"/>
-      <c r="E491" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F491" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G491" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H491" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I491" s="63"/>
-      <c r="J491" s="52"/>
-      <c r="K491" s="54">
-        <v>10</v>
-      </c>
-      <c r="L491" s="88">
-        <v>36982</v>
-      </c>
-      <c r="M491" s="52"/>
-      <c r="N491" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O491" s="53">
-        <v>0</v>
-      </c>
-      <c r="P491" s="53"/>
-      <c r="Q491" s="54">
-        <v>38</v>
-      </c>
-      <c r="R491" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S491" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T491" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U491" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V491" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W491" s="54"/>
-      <c r="X491" s="54"/>
-      <c r="Y491" s="54"/>
-      <c r="Z491" s="54"/>
-      <c r="AA491" s="52"/>
-      <c r="AB491" s="52"/>
-      <c r="AC491" s="52"/>
-      <c r="AD491" s="52"/>
-      <c r="AE491" s="52"/>
-      <c r="AF491" s="52"/>
-      <c r="AG491" s="52"/>
-      <c r="AH491" s="52"/>
-      <c r="AI491" s="52"/>
-      <c r="AJ491" s="52"/>
-      <c r="AK491" s="52"/>
-      <c r="AL491" s="52"/>
-      <c r="AM491" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN491" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="492" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A492" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B492" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C492" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D492" s="50"/>
-      <c r="E492" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F492" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G492" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H492" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I492" s="63"/>
-      <c r="J492" s="52"/>
-      <c r="K492" s="54">
-        <v>11</v>
-      </c>
-      <c r="L492" s="88">
-        <v>37073</v>
-      </c>
-      <c r="M492" s="52"/>
-      <c r="N492" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O492" s="53">
-        <v>0</v>
-      </c>
-      <c r="P492" s="53"/>
-      <c r="Q492" s="54">
-        <v>30.8</v>
-      </c>
-      <c r="R492" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S492" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T492" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U492" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V492" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W492" s="54"/>
-      <c r="X492" s="54"/>
-      <c r="Y492" s="54"/>
-      <c r="Z492" s="54"/>
-      <c r="AA492" s="52"/>
-      <c r="AB492" s="52"/>
-      <c r="AC492" s="52"/>
-      <c r="AD492" s="52"/>
-      <c r="AE492" s="52"/>
-      <c r="AF492" s="52"/>
-      <c r="AG492" s="52"/>
-      <c r="AH492" s="52"/>
-      <c r="AI492" s="52"/>
-      <c r="AJ492" s="52"/>
-      <c r="AK492" s="52"/>
-      <c r="AL492" s="52"/>
-      <c r="AM492" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN492" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="493" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A493" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B493" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C493" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D493" s="50"/>
-      <c r="E493" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F493" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G493" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H493" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I493" s="63"/>
-      <c r="J493" s="52"/>
-      <c r="K493" s="54">
-        <v>12</v>
-      </c>
-      <c r="L493" s="88">
-        <v>37165</v>
-      </c>
-      <c r="M493" s="52"/>
-      <c r="N493" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O493" s="53">
-        <v>0</v>
-      </c>
-      <c r="P493" s="53"/>
-      <c r="Q493" s="54">
-        <v>15.6</v>
-      </c>
-      <c r="R493" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S493" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T493" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U493" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V493" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W493" s="54"/>
-      <c r="X493" s="54"/>
-      <c r="Y493" s="54"/>
-      <c r="Z493" s="54"/>
-      <c r="AA493" s="52"/>
-      <c r="AB493" s="52"/>
-      <c r="AC493" s="52"/>
-      <c r="AD493" s="52"/>
-      <c r="AE493" s="52"/>
-      <c r="AF493" s="52"/>
-      <c r="AG493" s="52"/>
-      <c r="AH493" s="52"/>
-      <c r="AI493" s="52"/>
-      <c r="AJ493" s="52"/>
-      <c r="AK493" s="52"/>
-      <c r="AL493" s="52"/>
-      <c r="AM493" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN493" s="24" t="s">
-        <v>77</v>
-      </c>
+      <c r="AM481" s="40"/>
+      <c r="AN481" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
